--- a/support_files/ir_rating.xlsx
+++ b/support_files/ir_rating.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="406">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -253,15 +253,24 @@
     <t xml:space="preserve">81</t>
   </si>
   <si>
+    <t xml:space="preserve">MBNK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Диасофт</t>
   </si>
   <si>
     <t xml:space="preserve">80</t>
   </si>
   <si>
+    <t xml:space="preserve">DIAS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ламбумиз</t>
   </si>
   <si>
+    <t xml:space="preserve">LMBZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">VK</t>
   </si>
   <si>
@@ -274,9 +283,15 @@
     <t xml:space="preserve">Артген</t>
   </si>
   <si>
+    <t xml:space="preserve">ABIO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Делимобиль</t>
   </si>
   <si>
+    <t xml:space="preserve">DELI</t>
+  </si>
+  <si>
     <t xml:space="preserve">HeadHunter</t>
   </si>
   <si>
@@ -298,6 +313,9 @@
     <t xml:space="preserve">МГКЛ</t>
   </si>
   <si>
+    <t xml:space="preserve">MGKL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Лента</t>
   </si>
   <si>
@@ -622,6 +640,9 @@
     <t xml:space="preserve">МКБ</t>
   </si>
   <si>
+    <t xml:space="preserve">CBOM</t>
+  </si>
+  <si>
     <t xml:space="preserve">КуйбышевАзот</t>
   </si>
   <si>
@@ -724,7 +745,7 @@
     <t xml:space="preserve">32</t>
   </si>
   <si>
-    <t xml:space="preserve">TRNF</t>
+    <t xml:space="preserve">TRNFP</t>
   </si>
   <si>
     <t xml:space="preserve">Татнефть</t>
@@ -841,6 +862,9 @@
     <t xml:space="preserve">НМТП</t>
   </si>
   <si>
+    <t xml:space="preserve">NMTP</t>
+  </si>
+  <si>
     <t xml:space="preserve">ТГК-1</t>
   </si>
   <si>
@@ -916,6 +940,9 @@
     <t xml:space="preserve">Русолово</t>
   </si>
   <si>
+    <t xml:space="preserve">ROLO</t>
+  </si>
+  <si>
     <t xml:space="preserve">ЗаводДИОД</t>
   </si>
   <si>
@@ -985,6 +1012,9 @@
     <t xml:space="preserve">19</t>
   </si>
   <si>
+    <t xml:space="preserve">MSNG</t>
+  </si>
+  <si>
     <t xml:space="preserve">Красный октябрь</t>
   </si>
   <si>
@@ -1037,6 +1067,9 @@
   </si>
   <si>
     <t xml:space="preserve">Иркут</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRKT</t>
   </si>
   <si>
     <t xml:space="preserve">ОГК-2</t>
@@ -1295,7 +1328,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1310,6 +1343,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1867,1752 +1904,1785 @@
       <c r="B33" s="3" t="s">
         <v>76</v>
       </c>
+      <c r="C33" s="4" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>78</v>
+      <c r="C35" s="0" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>81</v>
+      <c r="C38" s="0" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C103" s="3"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C119" s="3"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C120" s="3"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C130" s="3"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
+      </c>
+      <c r="C135" s="0" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B137" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
+      </c>
+      <c r="C155" s="0" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>320</v>
+        <v>329</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/support_files/ir_rating.xlsx
+++ b/support_files/ir_rating.xlsx
@@ -442,7 +442,7 @@
     <t xml:space="preserve">Ленэнерго</t>
   </si>
   <si>
-    <t xml:space="preserve">LSNG</t>
+    <t xml:space="preserve">LSNGP</t>
   </si>
   <si>
     <t xml:space="preserve">Акрон</t>
@@ -1345,7 +1345,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1915,7 +1915,7 @@
       <c r="B34" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="3" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       <c r="B35" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="3" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       <c r="B37" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="3" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       <c r="B38" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="3" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       <c r="B41" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="3" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       <c r="B89" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C89" s="0" t="s">
+      <c r="C89" s="3" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       <c r="B135" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C135" s="0" t="s">
+      <c r="C135" s="3" t="s">
         <v>280</v>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       <c r="B155" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C155" s="0" t="s">
+      <c r="C155" s="3" t="s">
         <v>306</v>
       </c>
     </row>

--- a/support_files/ir_rating.xlsx
+++ b/support_files/ir_rating.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilyas\Documents\GitHub\invest_toolkit\support_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD0EFA3-3AA4-49C6-84C2-122EC544A2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="48" yWindow="744" windowWidth="30624" windowHeight="15768" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,1219 +27,1219 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="406">
   <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ticker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аэрофлот</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFLT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Астра</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASTR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Совкомбанк</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SVCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Промомед</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аренадата</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Озон Фармацевтика</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X5 Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СБЕР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SBER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Софтлайн</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мать и Дитя</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Норникель</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMKN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МосБиржа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ренессанс Страхование</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RENI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WHOOSH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WUSH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Займер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAYM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Европлан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Самолет</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMLT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Элемент</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МТС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Эталон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETLN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ВТБ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VTBR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Северсталь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Хэндерсон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNFG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Русагро</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAGR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ВсеИнструменты.ру</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VSEH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Т-Технологии</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">М.Видео</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MVID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Яндекс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YDEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МТС-Банк</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBNK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диасофт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ламбумиз</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMBZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VKCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Артген</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Делимобиль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HeadHunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети ЦП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRKP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МГКЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGKL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Лента</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АПРИ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ИнтерРАО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети Центр</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRKC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЮГК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ИНАРКТИКА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ФосАгро</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Полюс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLZL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CarMoney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Globaltrans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jetlend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ростелеком</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сегежа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGZH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FixPrice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ММК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЦИАН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNRU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Селигдар</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ленэнерго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSNG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Акрон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKRN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЭЛ5-Энерго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELFV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Магнит</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGNT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БСПБ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РусГидро</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Белуга</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BELU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети Урал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRKU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АЛРОСА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALRS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Европейская электротехника</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЛСР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSRG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Евротранс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUTR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТГК-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети СЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRKZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТМК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRMK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Юнипро</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Роснефть</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROSN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Генетико</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Новатэк</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVTK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пермьэнергосбыт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЕМС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МОЭСК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Газпром</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAZP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ДВМП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FESH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VEON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АФК Система</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Совкомфлот</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кристалл</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Распадская</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RASP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МКБ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КуйбышевАзот</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ММЦБ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наука-Связь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НКНХ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NKNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Казаньоргсинтез</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети Кубань</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KUBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети Томск</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EN+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РУСАЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OKEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КАМАЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Красноярскэнергосбыт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Якутскэнерго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети СК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СПБ Биржа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставропольэнергосбыт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АбрауДюрсо</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Росинтер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СОЛЛЕРС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ФСК-Россети</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Транснефть</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRNFP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Татнефть</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TATN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Магаданэнерго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рязаньэнергосбыт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети Сибирь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети Волга</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRKV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЛУКОЙЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LKOH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Россети Юг</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRKY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Калужская сбытовая компания</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ИК РУСС_ИНВЕСТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТНС энерго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Черкизово</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCHE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polymetal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Камчатскэенрго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Русснефть</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мечел</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTLR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Самараэнерго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Росдорбанк</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТНСэнерго Ростов-на-Дону</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нижнекамскшина</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТНС энерго НН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Левенгук</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Курганская ГК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НКХП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сахалинэнерго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НМТП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТГК-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Таттелеком</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЧКПЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Волгоградэнергосбыт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Башинформсвязь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТНС энерго Марий Эл</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТНС энерго Кубань</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ДЭК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОВК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Центр Международной Торговли</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WTCM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НЛМК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NLMK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МГТС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СМЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТНС энерго Ярославль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">УралСиб</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Донской завод радиодеталей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Светофор</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мордовэнергосбыт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Globaltruck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Русолово</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROLO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЗаводДИОД</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЯТЭК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Газпромнефть</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIBN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТГК-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОАК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТНС энерго Воронеж</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТКЗ Красный котельщик</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РКК Энергия</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Саратовэнерго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инград</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЧЗПСН-Профнастил</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тамбовэнергосбыт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QIWI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Костромская сбытовая компания</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Авангард</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПИК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIKK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мосэнерго</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSNG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Красный октябрь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Лензолото</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Росгосстрах</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Башнефть</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЮТэйр</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Варьеганнефтегаз</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НЕФАЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НПО Наука</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Банк Приморье</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Газпром газораспределение РНД</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Химпром</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЗИЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Белон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТЗА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Иркут</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRKT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОГК-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Южный Кузбасс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ижсталь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Арсагера</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Центральный телеграф</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Комбинат Южуралникель</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ГАЗ-сервис</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ГАЗКОН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Газ-Тек</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Банк Кузнецкий</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОМЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бурятзолото</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выборгский Судостроительный завод</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Косогорский мет. завод</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Владимирский химический завод</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РБК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBCM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мостотрест</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Фармсинтез</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ашинский метзавод</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аптеки 36,6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APTK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Славнефть-Мегионнефтегаз</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЧМК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Славнефть ЯНОС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Группа ГМС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЛЭСК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Астраханская энергосбытовая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОКС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Коршуновский ГОК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ковровский механический завод</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Саратовский НПЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ВСМПО-Ависма</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VSMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сургутнефтегаз</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Медиахолд</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РН-Западная Сибирь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Павловский автобус</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Уральская Кузница</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЗВЕЗДА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Росбанк</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Русгрэйн</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Детский Мир</t>
+    <t>name</t>
+  </si>
+  <si>
+    <t>rating</t>
+  </si>
+  <si>
+    <t>ticker</t>
+  </si>
+  <si>
+    <t>Аэрофлот</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>AFLT</t>
+  </si>
+  <si>
+    <t>Астра</t>
+  </si>
+  <si>
+    <t>ASTR</t>
+  </si>
+  <si>
+    <t>Positive Technologies</t>
+  </si>
+  <si>
+    <t>POSI</t>
+  </si>
+  <si>
+    <t>Совкомбанк</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>SVCB</t>
+  </si>
+  <si>
+    <t>Промомед</t>
+  </si>
+  <si>
+    <t>PRMD</t>
+  </si>
+  <si>
+    <t>Аренадата</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>Озон Фармацевтика</t>
+  </si>
+  <si>
+    <t>X5 Group</t>
+  </si>
+  <si>
+    <t>X5</t>
+  </si>
+  <si>
+    <t>СБЕР</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>SBER</t>
+  </si>
+  <si>
+    <t>Софтлайн</t>
+  </si>
+  <si>
+    <t>SOFL</t>
+  </si>
+  <si>
+    <t>Мать и Дитя</t>
+  </si>
+  <si>
+    <t>MDMG</t>
+  </si>
+  <si>
+    <t>Норникель</t>
+  </si>
+  <si>
+    <t>GMKN</t>
+  </si>
+  <si>
+    <t>МосБиржа</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>MOEX</t>
+  </si>
+  <si>
+    <t>Ренессанс Страхование</t>
+  </si>
+  <si>
+    <t>RENI</t>
+  </si>
+  <si>
+    <t>WHOOSH</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>WUSH</t>
+  </si>
+  <si>
+    <t>Займер</t>
+  </si>
+  <si>
+    <t>ZAYM</t>
+  </si>
+  <si>
+    <t>Европлан</t>
+  </si>
+  <si>
+    <t>LEAS</t>
+  </si>
+  <si>
+    <t>SFI</t>
+  </si>
+  <si>
+    <t>SFIN</t>
+  </si>
+  <si>
+    <t>Самолет</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>SMLT</t>
+  </si>
+  <si>
+    <t>Элемент</t>
+  </si>
+  <si>
+    <t>ELMT</t>
+  </si>
+  <si>
+    <t>МТС</t>
+  </si>
+  <si>
+    <t>MTSS</t>
+  </si>
+  <si>
+    <t>Эталон</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>ETLN</t>
+  </si>
+  <si>
+    <t>OZON</t>
+  </si>
+  <si>
+    <t>ВТБ</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>VTBR</t>
+  </si>
+  <si>
+    <t>Северсталь</t>
+  </si>
+  <si>
+    <t>CHMF</t>
+  </si>
+  <si>
+    <t>Хэндерсон</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>HNFG</t>
+  </si>
+  <si>
+    <t>Русагро</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>RAGR</t>
+  </si>
+  <si>
+    <t>ВсеИнструменты.ру</t>
+  </si>
+  <si>
+    <t>VSEH</t>
+  </si>
+  <si>
+    <t>Т-Технологии</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>М.Видео</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>MVID</t>
+  </si>
+  <si>
+    <t>Яндекс</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>YDEX</t>
+  </si>
+  <si>
+    <t>МТС-Банк</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>MBNK</t>
+  </si>
+  <si>
+    <t>Диасофт</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>DIAS</t>
+  </si>
+  <si>
+    <t>Ламбумиз</t>
+  </si>
+  <si>
+    <t>LMBZ</t>
+  </si>
+  <si>
+    <t>VK</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>VKCO</t>
+  </si>
+  <si>
+    <t>Артген</t>
+  </si>
+  <si>
+    <t>ABIO</t>
+  </si>
+  <si>
+    <t>Делимобиль</t>
+  </si>
+  <si>
+    <t>DELI</t>
+  </si>
+  <si>
+    <t>HeadHunter</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>HEAD</t>
+  </si>
+  <si>
+    <t>Россети ЦП</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>MRKP</t>
+  </si>
+  <si>
+    <t>МГКЛ</t>
+  </si>
+  <si>
+    <t>MGKL</t>
+  </si>
+  <si>
+    <t>Лента</t>
+  </si>
+  <si>
+    <t>LENT</t>
+  </si>
+  <si>
+    <t>IVA Technologies</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>АПРИ</t>
+  </si>
+  <si>
+    <t>ИнтерРАО</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>IRAO</t>
+  </si>
+  <si>
+    <t>Россети Центр</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>MRKC</t>
+  </si>
+  <si>
+    <t>ЮГК</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>ИНАРКТИКА</t>
+  </si>
+  <si>
+    <t>AQUA</t>
+  </si>
+  <si>
+    <t>ФосАгро</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>PHOR</t>
+  </si>
+  <si>
+    <t>Полюс</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>PLZL</t>
+  </si>
+  <si>
+    <t>CarMoney</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>Globaltrans</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Jetlend</t>
+  </si>
+  <si>
+    <t>Ростелеком</t>
+  </si>
+  <si>
+    <t>RTKM</t>
+  </si>
+  <si>
+    <t>Сегежа</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>SGZH</t>
+  </si>
+  <si>
+    <t>FixPrice</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>FIXR</t>
+  </si>
+  <si>
+    <t>ММК</t>
+  </si>
+  <si>
+    <t>MAGN</t>
+  </si>
+  <si>
+    <t>ЦИАН</t>
+  </si>
+  <si>
+    <t>CNRU</t>
+  </si>
+  <si>
+    <t>Селигдар</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>SELG</t>
+  </si>
+  <si>
+    <t>Ленэнерго</t>
+  </si>
+  <si>
+    <t>LSNG</t>
+  </si>
+  <si>
+    <t>Акрон</t>
+  </si>
+  <si>
+    <t>AKRN</t>
+  </si>
+  <si>
+    <t>ЭЛ5-Энерго</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>ELFV</t>
+  </si>
+  <si>
+    <t>Магнит</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>MGNT</t>
+  </si>
+  <si>
+    <t>БСПБ</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>BSPB</t>
+  </si>
+  <si>
+    <t>РусГидро</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>HYDR</t>
+  </si>
+  <si>
+    <t>Белуга</t>
+  </si>
+  <si>
+    <t>BELU</t>
+  </si>
+  <si>
+    <t>Россети Урал</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>MRKU</t>
+  </si>
+  <si>
+    <t>АЛРОСА</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>ALRS</t>
+  </si>
+  <si>
+    <t>Европейская электротехника</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>ЛСР</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>LSRG</t>
+  </si>
+  <si>
+    <t>Евротранс</t>
+  </si>
+  <si>
+    <t>EUTR</t>
+  </si>
+  <si>
+    <t>ТГК-14</t>
+  </si>
+  <si>
+    <t>Россети СЗ</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>MRKZ</t>
+  </si>
+  <si>
+    <t>ТМК</t>
+  </si>
+  <si>
+    <t>TRMK</t>
+  </si>
+  <si>
+    <t>Юнипро</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>UPRO</t>
+  </si>
+  <si>
+    <t>Роснефть</t>
+  </si>
+  <si>
+    <t>ROSN</t>
+  </si>
+  <si>
+    <t>Генетико</t>
+  </si>
+  <si>
+    <t>Новатэк</t>
+  </si>
+  <si>
+    <t>NVTK</t>
+  </si>
+  <si>
+    <t>Пермьэнергосбыт</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>PMSB</t>
+  </si>
+  <si>
+    <t>ЕМС</t>
+  </si>
+  <si>
+    <t>МОЭСК</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Газпром</t>
+  </si>
+  <si>
+    <t>GAZP</t>
+  </si>
+  <si>
+    <t>ДВМП</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>FESH</t>
+  </si>
+  <si>
+    <t>VEON</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>АФК Система</t>
+  </si>
+  <si>
+    <t>AFKS</t>
+  </si>
+  <si>
+    <t>Совкомфлот</t>
+  </si>
+  <si>
+    <t>FLOT</t>
+  </si>
+  <si>
+    <t>Кристалл</t>
+  </si>
+  <si>
+    <t>Распадская</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>RASP</t>
+  </si>
+  <si>
+    <t>МКБ</t>
+  </si>
+  <si>
+    <t>CBOM</t>
+  </si>
+  <si>
+    <t>КуйбышевАзот</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>ММЦБ</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Наука-Связь</t>
+  </si>
+  <si>
+    <t>НКНХ</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>NKNC</t>
+  </si>
+  <si>
+    <t>Казаньоргсинтез</t>
+  </si>
+  <si>
+    <t>Россети Кубань</t>
+  </si>
+  <si>
+    <t>KUBE</t>
+  </si>
+  <si>
+    <t>Россети Томск</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>TORS</t>
+  </si>
+  <si>
+    <t>EN+</t>
+  </si>
+  <si>
+    <t>ENPG</t>
+  </si>
+  <si>
+    <t>РУСАЛ</t>
+  </si>
+  <si>
+    <t>RUAL</t>
+  </si>
+  <si>
+    <t>OKEY</t>
+  </si>
+  <si>
+    <t>КАМАЗ</t>
+  </si>
+  <si>
+    <t>Красноярскэнергосбыт</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Якутскэнерго</t>
+  </si>
+  <si>
+    <t>Россети СК</t>
+  </si>
+  <si>
+    <t>СПБ Биржа</t>
+  </si>
+  <si>
+    <t>SPBE</t>
+  </si>
+  <si>
+    <t>Ставропольэнергосбыт</t>
+  </si>
+  <si>
+    <t>АбрауДюрсо</t>
+  </si>
+  <si>
+    <t>Росинтер</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>СОЛЛЕРС</t>
+  </si>
+  <si>
+    <t>ФСК-Россети</t>
+  </si>
+  <si>
+    <t>Транснефть</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>TRNFP</t>
+  </si>
+  <si>
+    <t>Татнефть</t>
+  </si>
+  <si>
+    <t>TATN</t>
+  </si>
+  <si>
+    <t>Магаданэнерго</t>
+  </si>
+  <si>
+    <t>Рязаньэнергосбыт</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Россети Сибирь</t>
+  </si>
+  <si>
+    <t>MRKS</t>
+  </si>
+  <si>
+    <t>Россети Волга</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>MRKV</t>
+  </si>
+  <si>
+    <t>ЛУКОЙЛ</t>
+  </si>
+  <si>
+    <t>LKOH</t>
+  </si>
+  <si>
+    <t>Россети Юг</t>
+  </si>
+  <si>
+    <t>MRKY</t>
+  </si>
+  <si>
+    <t>Калужская сбытовая компания</t>
+  </si>
+  <si>
+    <t>ИК РУСС_ИНВЕСТ</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>ТНС энерго</t>
+  </si>
+  <si>
+    <t>Черкизово</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>GCHE</t>
+  </si>
+  <si>
+    <t>Polymetal</t>
+  </si>
+  <si>
+    <t>Камчатскэенрго</t>
+  </si>
+  <si>
+    <t>Русснефть</t>
+  </si>
+  <si>
+    <t>Мечел</t>
+  </si>
+  <si>
+    <t>MTLR</t>
+  </si>
+  <si>
+    <t>Самараэнерго</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Росдорбанк</t>
+  </si>
+  <si>
+    <t>ТНСэнерго Ростов-на-Дону</t>
+  </si>
+  <si>
+    <t>Нижнекамскшина</t>
+  </si>
+  <si>
+    <t>ТНС энерго НН</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Левенгук</t>
+  </si>
+  <si>
+    <t>Курганская ГК</t>
+  </si>
+  <si>
+    <t>НКХП</t>
+  </si>
+  <si>
+    <t>Сахалинэнерго</t>
+  </si>
+  <si>
+    <t>НМТП</t>
+  </si>
+  <si>
+    <t>NMTP</t>
+  </si>
+  <si>
+    <t>ТГК-1</t>
+  </si>
+  <si>
+    <t>Таттелеком</t>
+  </si>
+  <si>
+    <t>ЧКПЗ</t>
+  </si>
+  <si>
+    <t>Волгоградэнергосбыт</t>
+  </si>
+  <si>
+    <t>Башинформсвязь</t>
+  </si>
+  <si>
+    <t>ТНС энерго Марий Эл</t>
+  </si>
+  <si>
+    <t>ТНС энерго Кубань</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>ДЭК</t>
+  </si>
+  <si>
+    <t>ОВК</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Центр Международной Торговли</t>
+  </si>
+  <si>
+    <t>WTCM</t>
+  </si>
+  <si>
+    <t>НЛМК</t>
+  </si>
+  <si>
+    <t>NLMK</t>
+  </si>
+  <si>
+    <t>МГТС</t>
+  </si>
+  <si>
+    <t>СМЗ</t>
+  </si>
+  <si>
+    <t>ТНС энерго Ярославль</t>
+  </si>
+  <si>
+    <t>УралСиб</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Донской завод радиодеталей</t>
+  </si>
+  <si>
+    <t>Светофор</t>
+  </si>
+  <si>
+    <t>Мордовэнергосбыт</t>
+  </si>
+  <si>
+    <t>Globaltruck</t>
+  </si>
+  <si>
+    <t>Русолово</t>
+  </si>
+  <si>
+    <t>ROLO</t>
+  </si>
+  <si>
+    <t>ЗаводДИОД</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>ЯТЭК</t>
+  </si>
+  <si>
+    <t>Газпромнефть</t>
+  </si>
+  <si>
+    <t>SIBN</t>
+  </si>
+  <si>
+    <t>ТГК-2</t>
+  </si>
+  <si>
+    <t>ОАК</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>ТНС энерго Воронеж</t>
+  </si>
+  <si>
+    <t>ТКЗ Красный котельщик</t>
+  </si>
+  <si>
+    <t>РКК Энергия</t>
+  </si>
+  <si>
+    <t>Саратовэнерго</t>
+  </si>
+  <si>
+    <t>Инград</t>
+  </si>
+  <si>
+    <t>ЧЗПСН-Профнастил</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Тамбовэнергосбыт</t>
+  </si>
+  <si>
+    <t>QIWI</t>
+  </si>
+  <si>
+    <t>Костромская сбытовая компания</t>
+  </si>
+  <si>
+    <t>Авангард</t>
+  </si>
+  <si>
+    <t>ПИК</t>
+  </si>
+  <si>
+    <t>PIKK</t>
+  </si>
+  <si>
+    <t>Мосэнерго</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>MSNG</t>
+  </si>
+  <si>
+    <t>Красный октябрь</t>
+  </si>
+  <si>
+    <t>Лензолото</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Росгосстрах</t>
+  </si>
+  <si>
+    <t>Башнефть</t>
+  </si>
+  <si>
+    <t>BANE</t>
+  </si>
+  <si>
+    <t>ЮТэйр</t>
+  </si>
+  <si>
+    <t>Варьеганнефтегаз</t>
+  </si>
+  <si>
+    <t>НЕФАЗ</t>
+  </si>
+  <si>
+    <t>НПО Наука</t>
+  </si>
+  <si>
+    <t>Банк Приморье</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Газпром газораспределение РНД</t>
+  </si>
+  <si>
+    <t>Химпром</t>
+  </si>
+  <si>
+    <t>ЗИЛ</t>
+  </si>
+  <si>
+    <t>Белон</t>
+  </si>
+  <si>
+    <t>ТЗА</t>
+  </si>
+  <si>
+    <t>Иркут</t>
+  </si>
+  <si>
+    <t>IRKT</t>
+  </si>
+  <si>
+    <t>ОГК-2</t>
+  </si>
+  <si>
+    <t>Южный Кузбасс</t>
+  </si>
+  <si>
+    <t>Ижсталь</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Арсагера</t>
+  </si>
+  <si>
+    <t>Центральный телеграф</t>
+  </si>
+  <si>
+    <t>Комбинат Южуралникель</t>
+  </si>
+  <si>
+    <t>ГАЗ-сервис</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>ГАЗКОН</t>
+  </si>
+  <si>
+    <t>Газ-Тек</t>
+  </si>
+  <si>
+    <t>Банк Кузнецкий</t>
+  </si>
+  <si>
+    <t>ОМЗ</t>
+  </si>
+  <si>
+    <t>Бурятзолото</t>
+  </si>
+  <si>
+    <t>Выборгский Судостроительный завод</t>
+  </si>
+  <si>
+    <t>Косогорский мет. завод</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Владимирский химический завод</t>
+  </si>
+  <si>
+    <t>РБК</t>
+  </si>
+  <si>
+    <t>RBCM</t>
+  </si>
+  <si>
+    <t>Мостотрест</t>
+  </si>
+  <si>
+    <t>Фармсинтез</t>
+  </si>
+  <si>
+    <t>Ашинский метзавод</t>
+  </si>
+  <si>
+    <t>Аптеки 36,6</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>APTK</t>
+  </si>
+  <si>
+    <t>Славнефть-Мегионнефтегаз</t>
+  </si>
+  <si>
+    <t>ЧМК</t>
+  </si>
+  <si>
+    <t>Славнефть ЯНОС</t>
+  </si>
+  <si>
+    <t>Группа ГМС</t>
+  </si>
+  <si>
+    <t>ЛЭСК</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Астраханская энергосбытовая</t>
+  </si>
+  <si>
+    <t>ОКС</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Коршуновский ГОК</t>
+  </si>
+  <si>
+    <t>Ковровский механический завод</t>
+  </si>
+  <si>
+    <t>Саратовский НПЗ</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>ВСМПО-Ависма</t>
+  </si>
+  <si>
+    <t>VSMO</t>
+  </si>
+  <si>
+    <t>Сургутнефтегаз</t>
+  </si>
+  <si>
+    <t>SNGS</t>
+  </si>
+  <si>
+    <t>Медиахолд</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>РН-Западная Сибирь</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Павловский автобус</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Уральская Кузница</t>
+  </si>
+  <si>
+    <t>ЗВЕЗДА</t>
+  </si>
+  <si>
+    <t>Росбанк</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Русгрэйн</t>
+  </si>
+  <si>
+    <t>Детский Мир</t>
   </si>
   <si>
     <t xml:space="preserve">ГАЗ </t>
@@ -1243,11 +1248,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1256,22 +1258,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1288,115 +1275,95 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1404,12 +1371,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1438,7 +1405,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1459,7 +1426,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1510,7 +1477,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1528,26 +1495,25 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C228"/>
-  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.41"/>
+    <col min="1" max="1" width="32.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1569,7 +1535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1580,7 +1546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1591,7 +1557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1602,7 +1568,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1613,7 +1579,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -1624,7 +1590,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1633,7 +1599,7 @@
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -1644,7 +1610,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1655,7 +1621,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -1666,7 +1632,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1677,7 +1643,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -1688,7 +1654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -1699,7 +1665,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -1710,7 +1676,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -1721,7 +1687,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>37</v>
       </c>
@@ -1732,7 +1698,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>39</v>
       </c>
@@ -1743,7 +1709,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>41</v>
       </c>
@@ -1754,7 +1720,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
@@ -1765,7 +1731,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
@@ -1776,7 +1742,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>48</v>
       </c>
@@ -1787,7 +1753,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>50</v>
       </c>
@@ -1798,7 +1764,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>53</v>
       </c>
@@ -1809,7 +1775,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -1820,7 +1786,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>57</v>
       </c>
@@ -1831,7 +1797,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>59</v>
       </c>
@@ -1842,7 +1808,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>62</v>
       </c>
@@ -1853,7 +1819,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>65</v>
       </c>
@@ -1864,7 +1830,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>67</v>
       </c>
@@ -1875,7 +1841,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>69</v>
       </c>
@@ -1886,7 +1852,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>72</v>
       </c>
@@ -1897,7 +1863,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>75</v>
       </c>
@@ -1908,29 +1874,29 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>83</v>
       </c>
@@ -1941,29 +1907,29 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>90</v>
       </c>
@@ -1974,7 +1940,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>93</v>
       </c>
@@ -1985,18 +1951,18 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>98</v>
       </c>
@@ -2007,7 +1973,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>100</v>
       </c>
@@ -2015,7 +1981,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>102</v>
       </c>
@@ -2023,7 +1989,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>103</v>
       </c>
@@ -2034,7 +2000,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>106</v>
       </c>
@@ -2045,7 +2011,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>109</v>
       </c>
@@ -2053,7 +2019,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>111</v>
       </c>
@@ -2064,7 +2030,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>113</v>
       </c>
@@ -2075,7 +2041,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>116</v>
       </c>
@@ -2086,7 +2052,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>119</v>
       </c>
@@ -2094,7 +2060,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>121</v>
       </c>
@@ -2102,7 +2068,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>123</v>
       </c>
@@ -2110,7 +2076,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>124</v>
       </c>
@@ -2121,7 +2087,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>126</v>
       </c>
@@ -2132,7 +2098,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>129</v>
       </c>
@@ -2143,7 +2109,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>132</v>
       </c>
@@ -2154,7 +2120,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>134</v>
       </c>
@@ -2165,7 +2131,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>136</v>
       </c>
@@ -2176,7 +2142,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>139</v>
       </c>
@@ -2187,7 +2153,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>141</v>
       </c>
@@ -2198,7 +2164,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>143</v>
       </c>
@@ -2209,7 +2175,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>146</v>
       </c>
@@ -2220,7 +2186,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>149</v>
       </c>
@@ -2231,7 +2197,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>152</v>
       </c>
@@ -2242,7 +2208,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>155</v>
       </c>
@@ -2253,7 +2219,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>157</v>
       </c>
@@ -2264,7 +2230,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>160</v>
       </c>
@@ -2275,7 +2241,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>163</v>
       </c>
@@ -2283,7 +2249,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>165</v>
       </c>
@@ -2294,7 +2260,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>168</v>
       </c>
@@ -2305,7 +2271,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>170</v>
       </c>
@@ -2313,7 +2279,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>171</v>
       </c>
@@ -2324,7 +2290,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>174</v>
       </c>
@@ -2335,7 +2301,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>176</v>
       </c>
@@ -2346,7 +2312,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>179</v>
       </c>
@@ -2357,7 +2323,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>181</v>
       </c>
@@ -2365,7 +2331,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>182</v>
       </c>
@@ -2376,7 +2342,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>184</v>
       </c>
@@ -2387,7 +2353,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>187</v>
       </c>
@@ -2395,7 +2361,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>188</v>
       </c>
@@ -2403,7 +2369,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>190</v>
       </c>
@@ -2414,7 +2380,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>192</v>
       </c>
@@ -2425,7 +2391,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>195</v>
       </c>
@@ -2433,7 +2399,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>197</v>
       </c>
@@ -2444,7 +2410,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>199</v>
       </c>
@@ -2455,7 +2421,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>201</v>
       </c>
@@ -2463,7 +2429,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>202</v>
       </c>
@@ -2474,18 +2440,18 @@
         <v>204</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C89" s="0" t="s">
+      <c r="C89" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>207</v>
       </c>
@@ -2493,7 +2459,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>209</v>
       </c>
@@ -2501,7 +2467,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>211</v>
       </c>
@@ -2509,7 +2475,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>212</v>
       </c>
@@ -2520,7 +2486,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>215</v>
       </c>
@@ -2528,7 +2494,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>216</v>
       </c>
@@ -2539,7 +2505,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>218</v>
       </c>
@@ -2550,7 +2516,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>221</v>
       </c>
@@ -2561,7 +2527,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>223</v>
       </c>
@@ -2572,7 +2538,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>225</v>
       </c>
@@ -2583,7 +2549,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>226</v>
       </c>
@@ -2591,7 +2557,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>227</v>
       </c>
@@ -2599,7 +2565,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>229</v>
       </c>
@@ -2607,7 +2573,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>230</v>
       </c>
@@ -2616,7 +2582,7 @@
       </c>
       <c r="C103" s="3"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>231</v>
       </c>
@@ -2627,7 +2593,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>233</v>
       </c>
@@ -2635,7 +2601,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>234</v>
       </c>
@@ -2643,7 +2609,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>235</v>
       </c>
@@ -2651,7 +2617,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>237</v>
       </c>
@@ -2659,7 +2625,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>238</v>
       </c>
@@ -2667,7 +2633,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>239</v>
       </c>
@@ -2678,7 +2644,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>242</v>
       </c>
@@ -2689,7 +2655,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>244</v>
       </c>
@@ -2697,7 +2663,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>245</v>
       </c>
@@ -2705,7 +2671,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>247</v>
       </c>
@@ -2716,7 +2682,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>249</v>
       </c>
@@ -2727,7 +2693,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>252</v>
       </c>
@@ -2738,7 +2704,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>254</v>
       </c>
@@ -2749,7 +2715,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>256</v>
       </c>
@@ -2757,7 +2723,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>257</v>
       </c>
@@ -2766,7 +2732,7 @@
       </c>
       <c r="C119" s="3"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>259</v>
       </c>
@@ -2775,7 +2741,7 @@
       </c>
       <c r="C120" s="3"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>260</v>
       </c>
@@ -2786,7 +2752,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>263</v>
       </c>
@@ -2794,7 +2760,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>264</v>
       </c>
@@ -2802,7 +2768,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>265</v>
       </c>
@@ -2810,7 +2776,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>266</v>
       </c>
@@ -2821,7 +2787,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>268</v>
       </c>
@@ -2829,7 +2795,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>270</v>
       </c>
@@ -2837,7 +2803,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>271</v>
       </c>
@@ -2845,7 +2811,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>272</v>
       </c>
@@ -2853,7 +2819,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>273</v>
       </c>
@@ -2862,7 +2828,7 @@
       </c>
       <c r="C130" s="3"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>275</v>
       </c>
@@ -2870,7 +2836,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>276</v>
       </c>
@@ -2878,7 +2844,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>277</v>
       </c>
@@ -2886,7 +2852,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>278</v>
       </c>
@@ -2894,18 +2860,18 @@
         <v>274</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>279</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C135" s="0" t="s">
+      <c r="C135" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>281</v>
       </c>
@@ -2913,7 +2879,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>282</v>
       </c>
@@ -2921,7 +2887,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>283</v>
       </c>
@@ -2929,7 +2895,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>284</v>
       </c>
@@ -2937,7 +2903,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>285</v>
       </c>
@@ -2945,7 +2911,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>286</v>
       </c>
@@ -2953,7 +2919,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>287</v>
       </c>
@@ -2961,7 +2927,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>289</v>
       </c>
@@ -2969,7 +2935,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>290</v>
       </c>
@@ -2977,7 +2943,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>292</v>
       </c>
@@ -2988,7 +2954,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>294</v>
       </c>
@@ -2999,7 +2965,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>296</v>
       </c>
@@ -3007,7 +2973,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>297</v>
       </c>
@@ -3015,7 +2981,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>298</v>
       </c>
@@ -3023,7 +2989,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>299</v>
       </c>
@@ -3031,7 +2997,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>301</v>
       </c>
@@ -3039,7 +3005,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>302</v>
       </c>
@@ -3047,7 +3013,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>303</v>
       </c>
@@ -3055,7 +3021,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>304</v>
       </c>
@@ -3063,18 +3029,18 @@
         <v>300</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>305</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C155" s="0" t="s">
+      <c r="C155" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>307</v>
       </c>
@@ -3082,7 +3048,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>309</v>
       </c>
@@ -3090,7 +3056,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>310</v>
       </c>
@@ -3101,7 +3067,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>312</v>
       </c>
@@ -3109,7 +3075,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>313</v>
       </c>
@@ -3117,7 +3083,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>315</v>
       </c>
@@ -3125,7 +3091,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>316</v>
       </c>
@@ -3133,7 +3099,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>317</v>
       </c>
@@ -3141,7 +3107,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>318</v>
       </c>
@@ -3149,7 +3115,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>319</v>
       </c>
@@ -3157,7 +3123,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>320</v>
       </c>
@@ -3165,7 +3131,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>322</v>
       </c>
@@ -3173,7 +3139,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>323</v>
       </c>
@@ -3181,7 +3147,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>324</v>
       </c>
@@ -3189,7 +3155,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>325</v>
       </c>
@@ -3197,7 +3163,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>326</v>
       </c>
@@ -3208,7 +3174,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>328</v>
       </c>
@@ -3219,7 +3185,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>331</v>
       </c>
@@ -3227,7 +3193,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>332</v>
       </c>
@@ -3235,7 +3201,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>334</v>
       </c>
@@ -3243,7 +3209,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>335</v>
       </c>
@@ -3254,7 +3220,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>337</v>
       </c>
@@ -3262,7 +3228,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>338</v>
       </c>
@@ -3270,7 +3236,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>339</v>
       </c>
@@ -3278,7 +3244,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>340</v>
       </c>
@@ -3286,7 +3252,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>341</v>
       </c>
@@ -3294,7 +3260,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>343</v>
       </c>
@@ -3302,7 +3268,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>344</v>
       </c>
@@ -3310,7 +3276,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>345</v>
       </c>
@@ -3318,7 +3284,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>346</v>
       </c>
@@ -3326,7 +3292,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>347</v>
       </c>
@@ -3334,7 +3300,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>348</v>
       </c>
@@ -3345,7 +3311,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>350</v>
       </c>
@@ -3353,7 +3319,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>351</v>
       </c>
@@ -3361,7 +3327,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>352</v>
       </c>
@@ -3369,7 +3335,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>354</v>
       </c>
@@ -3377,7 +3343,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>355</v>
       </c>
@@ -3385,7 +3351,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>356</v>
       </c>
@@ -3393,7 +3359,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>357</v>
       </c>
@@ -3401,7 +3367,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>359</v>
       </c>
@@ -3409,7 +3375,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>360</v>
       </c>
@@ -3417,7 +3383,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>361</v>
       </c>
@@ -3425,7 +3391,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>362</v>
       </c>
@@ -3433,7 +3399,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>363</v>
       </c>
@@ -3441,7 +3407,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>364</v>
       </c>
@@ -3449,7 +3415,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>365</v>
       </c>
@@ -3457,7 +3423,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>367</v>
       </c>
@@ -3465,7 +3431,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>368</v>
       </c>
@@ -3476,7 +3442,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>370</v>
       </c>
@@ -3484,7 +3450,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>371</v>
       </c>
@@ -3492,7 +3458,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>372</v>
       </c>
@@ -3500,7 +3466,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>373</v>
       </c>
@@ -3511,7 +3477,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>376</v>
       </c>
@@ -3519,7 +3485,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>377</v>
       </c>
@@ -3527,7 +3493,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>378</v>
       </c>
@@ -3535,7 +3501,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>379</v>
       </c>
@@ -3543,7 +3509,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>380</v>
       </c>
@@ -3551,7 +3517,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>382</v>
       </c>
@@ -3559,7 +3525,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>383</v>
       </c>
@@ -3567,7 +3533,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>385</v>
       </c>
@@ -3575,7 +3541,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>386</v>
       </c>
@@ -3583,7 +3549,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>387</v>
       </c>
@@ -3591,7 +3557,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>389</v>
       </c>
@@ -3602,7 +3568,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>391</v>
       </c>
@@ -3613,7 +3579,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>393</v>
       </c>
@@ -3621,7 +3587,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>395</v>
       </c>
@@ -3629,7 +3595,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>397</v>
       </c>
@@ -3637,7 +3603,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>399</v>
       </c>
@@ -3645,7 +3611,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>400</v>
       </c>
@@ -3653,7 +3619,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>401</v>
       </c>
@@ -3661,7 +3627,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>403</v>
       </c>
@@ -3669,7 +3635,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>404</v>
       </c>
@@ -3677,7 +3643,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>405</v>
       </c>
@@ -3686,12 +3652,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/support_files/ir_rating.xlsx
+++ b/support_files/ir_rating.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilyas\Documents\GitHub\invest_toolkit\support_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FE38B4-D204-44A8-8D8E-D1C9951B0AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E660BD-F8BD-4B86-B1A9-8759D295A286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48" yWindow="744" windowWidth="30624" windowHeight="15768" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="430">
   <si>
     <t>name</t>
   </si>
@@ -324,15 +324,6 @@
     <t>CarMoney</t>
   </si>
   <si>
-    <t>Globaltrans</t>
-  </si>
-  <si>
-    <t>Jetlend</t>
-  </si>
-  <si>
-    <t>JETL</t>
-  </si>
-  <si>
     <t>Ростелеком</t>
   </si>
   <si>
@@ -426,9 +417,6 @@
     <t>Европейская электротехника</t>
   </si>
   <si>
-    <t>EELT </t>
-  </si>
-  <si>
     <t>ЛСР</t>
   </si>
   <si>
@@ -444,9 +432,6 @@
     <t>ТГК-14</t>
   </si>
   <si>
-    <t>TGKN </t>
-  </si>
-  <si>
     <t>Россети СЗ</t>
   </si>
   <si>
@@ -552,12 +537,6 @@
     <t>Казаньоргсинтез</t>
   </si>
   <si>
-    <t>Россети Кубань</t>
-  </si>
-  <si>
-    <t>KUBE</t>
-  </si>
-  <si>
     <t>Россети Томск</t>
   </si>
   <si>
@@ -672,9 +651,6 @@
     <t>GCHE</t>
   </si>
   <si>
-    <t>Polymetal</t>
-  </si>
-  <si>
     <t>Камчатскэенрго</t>
   </si>
   <si>
@@ -828,12 +804,6 @@
     <t>Тамбовэнергосбыт</t>
   </si>
   <si>
-    <t>QIWI</t>
-  </si>
-  <si>
-    <t>Костромская сбытовая компания</t>
-  </si>
-  <si>
     <t>Авангард</t>
   </si>
   <si>
@@ -939,9 +909,6 @@
     <t>Выборгский Судостроительный завод</t>
   </si>
   <si>
-    <t>Косогорский мет. завод</t>
-  </si>
-  <si>
     <t>Владимирский химический завод</t>
   </si>
   <si>
@@ -975,18 +942,12 @@
     <t>Славнефть ЯНОС</t>
   </si>
   <si>
-    <t>Группа ГМС</t>
-  </si>
-  <si>
     <t>ЛЭСК</t>
   </si>
   <si>
     <t>Астраханская энергосбытовая</t>
   </si>
   <si>
-    <t>ОКС</t>
-  </si>
-  <si>
     <t>Коршуновский ГОК</t>
   </si>
   <si>
@@ -1008,9 +969,6 @@
     <t>SNGS</t>
   </si>
   <si>
-    <t>Медиахолд</t>
-  </si>
-  <si>
     <t>РН-Западная Сибирь</t>
   </si>
   <si>
@@ -1023,24 +981,12 @@
     <t>ЗВЕЗДА</t>
   </si>
   <si>
-    <t>Росбанк</t>
-  </si>
-  <si>
-    <t>Русгрэйн</t>
-  </si>
-  <si>
-    <t>Детский Мир</t>
-  </si>
-  <si>
     <t>APRI</t>
   </si>
   <si>
     <t>CARM</t>
   </si>
   <si>
-    <t>GLTR</t>
-  </si>
-  <si>
     <t>GECO</t>
   </si>
   <si>
@@ -1104,9 +1050,6 @@
     <t>TNSE</t>
   </si>
   <si>
-    <t>POLY</t>
-  </si>
-  <si>
     <t>KCHE</t>
   </si>
   <si>
@@ -1224,9 +1167,6 @@
     <t>TASB</t>
   </si>
   <si>
-    <t>KTSB</t>
-  </si>
-  <si>
     <t>AVAN</t>
   </si>
   <si>
@@ -1305,12 +1245,6 @@
     <t>BRZL</t>
   </si>
   <si>
-    <t>VSYD</t>
-  </si>
-  <si>
-    <t>KMTZ</t>
-  </si>
-  <si>
     <t>VLHZ</t>
   </si>
   <si>
@@ -1332,18 +1266,12 @@
     <t>JNOS</t>
   </si>
   <si>
-    <t>HMSG</t>
-  </si>
-  <si>
     <t>LPSB</t>
   </si>
   <si>
     <t>ASSB</t>
   </si>
   <si>
-    <t>UCSS</t>
-  </si>
-  <si>
     <t>KOGK</t>
   </si>
   <si>
@@ -1353,9 +1281,6 @@
     <t>KRKNP</t>
   </si>
   <si>
-    <t>ODVA</t>
-  </si>
-  <si>
     <t>CHGZ</t>
   </si>
   <si>
@@ -1368,15 +1293,6 @@
     <t>ZVEZ</t>
   </si>
   <si>
-    <t>ROSB</t>
-  </si>
-  <si>
-    <t>RUGR</t>
-  </si>
-  <si>
-    <t>DSKY</t>
-  </si>
-  <si>
     <t>ГАЗ</t>
   </si>
   <si>
@@ -1390,6 +1306,15 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>EELT</t>
+  </si>
+  <si>
+    <t>TGKN</t>
+  </si>
+  <si>
+    <t>VSYDP</t>
   </si>
 </sst>
 </file>
@@ -1653,7 +1578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D228"/>
+  <dimension ref="A1:D215"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.44140625" style="1" customWidth="1"/>
@@ -1669,10 +1594,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>452</v>
+        <v>424</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>454</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
@@ -1683,7 +1608,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D2" s="3">
         <v>97</v>
@@ -1697,7 +1622,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D3" s="3">
         <v>97</v>
@@ -1711,7 +1636,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D4" s="3">
         <v>97</v>
@@ -1725,7 +1650,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D5" s="3">
         <v>96</v>
@@ -1739,7 +1664,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D6" s="3">
         <v>96</v>
@@ -1753,7 +1678,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D7" s="3">
         <v>96</v>
@@ -1767,7 +1692,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D8" s="3">
         <v>96</v>
@@ -1781,7 +1706,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D9" s="3">
         <v>96</v>
@@ -1795,7 +1720,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D10" s="3">
         <v>95</v>
@@ -1809,7 +1734,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D11" s="3">
         <v>95</v>
@@ -1823,7 +1748,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D12" s="3">
         <v>95</v>
@@ -1837,7 +1762,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D13" s="3">
         <v>95</v>
@@ -1851,7 +1776,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D14" s="3">
         <v>94</v>
@@ -1865,7 +1790,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D15" s="3">
         <v>94</v>
@@ -1879,7 +1804,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D16" s="3">
         <v>93</v>
@@ -1893,7 +1818,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D17" s="3">
         <v>93</v>
@@ -1907,7 +1832,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D18" s="3">
         <v>93</v>
@@ -1921,7 +1846,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D19" s="3">
         <v>93</v>
@@ -1935,7 +1860,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D20" s="3">
         <v>90</v>
@@ -1949,7 +1874,7 @@
         <v>41</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D21" s="3">
         <v>90</v>
@@ -1963,7 +1888,7 @@
         <v>43</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D22" s="3">
         <v>90</v>
@@ -1977,7 +1902,7 @@
         <v>45</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D23" s="3">
         <v>89</v>
@@ -1991,7 +1916,7 @@
         <v>46</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D24" s="3">
         <v>89</v>
@@ -2005,7 +1930,7 @@
         <v>48</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D25" s="3">
         <v>87</v>
@@ -2019,7 +1944,7 @@
         <v>50</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D26" s="3">
         <v>87</v>
@@ -2033,7 +1958,7 @@
         <v>52</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D27" s="3">
         <v>86</v>
@@ -2047,7 +1972,7 @@
         <v>54</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D28" s="3">
         <v>85</v>
@@ -2061,7 +1986,7 @@
         <v>56</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D29" s="3">
         <v>85</v>
@@ -2075,7 +2000,7 @@
         <v>58</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D30" s="3">
         <v>85</v>
@@ -2089,7 +2014,7 @@
         <v>60</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D31" s="3">
         <v>84</v>
@@ -2103,7 +2028,7 @@
         <v>62</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D32" s="3">
         <v>82</v>
@@ -2117,7 +2042,7 @@
         <v>64</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D33" s="3">
         <v>81</v>
@@ -2131,7 +2056,7 @@
         <v>66</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D34" s="3">
         <v>80</v>
@@ -2145,7 +2070,7 @@
         <v>68</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D35" s="3">
         <v>80</v>
@@ -2159,7 +2084,7 @@
         <v>70</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D36" s="3">
         <v>77</v>
@@ -2173,7 +2098,7 @@
         <v>72</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D37" s="3">
         <v>77</v>
@@ -2187,7 +2112,7 @@
         <v>74</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D38" s="3">
         <v>77</v>
@@ -2201,7 +2126,7 @@
         <v>76</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D39" s="3">
         <v>75</v>
@@ -2215,7 +2140,7 @@
         <v>78</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D40" s="3">
         <v>74</v>
@@ -2229,7 +2154,7 @@
         <v>80</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D41" s="3">
         <v>74</v>
@@ -2243,7 +2168,7 @@
         <v>82</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D42" s="3">
         <v>74</v>
@@ -2257,7 +2182,7 @@
         <v>84</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D43" s="3">
         <v>73</v>
@@ -2268,10 +2193,10 @@
         <v>85</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D44" s="3">
         <v>73</v>
@@ -2285,7 +2210,7 @@
         <v>87</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D45" s="3">
         <v>72</v>
@@ -2299,7 +2224,7 @@
         <v>89</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D46" s="3">
         <v>71</v>
@@ -2313,7 +2238,7 @@
         <v>91</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D47" s="3">
         <v>70</v>
@@ -2327,7 +2252,7 @@
         <v>93</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D48" s="3">
         <v>70</v>
@@ -2341,7 +2266,7 @@
         <v>95</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D49" s="3">
         <v>69</v>
@@ -2355,7 +2280,7 @@
         <v>97</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D50" s="3">
         <v>67</v>
@@ -2366,10 +2291,10 @@
         <v>98</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D51" s="3">
         <v>66</v>
@@ -2379,11 +2304,11 @@
       <c r="A52" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>337</v>
+      <c r="B52" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D52" s="3">
         <v>65</v>
@@ -2391,55 +2316,55 @@
     </row>
     <row r="53" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B53" s="5" t="s">
         <v>101</v>
       </c>
+      <c r="B53" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="C53" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D53" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D54" s="3">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D55" s="3">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D56" s="3">
         <v>63</v>
@@ -2447,41 +2372,41 @@
     </row>
     <row r="57" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D57" s="3">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D58" s="3">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D59" s="3">
         <v>62</v>
@@ -2489,114 +2414,114 @@
     </row>
     <row r="60" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D60" s="3">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D61" s="3">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D62" s="3">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D63" s="3">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D64" s="3">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D65" s="3">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D66" s="3">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B67" s="3" t="s">
         <v>129</v>
       </c>
+      <c r="B67" s="5" t="s">
+        <v>427</v>
+      </c>
       <c r="C67" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D67" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
@@ -2607,35 +2532,35 @@
         <v>131</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D68" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D69" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>135</v>
+      <c r="B70" s="5" t="s">
+        <v>428</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D70" s="3">
         <v>47</v>
@@ -2643,69 +2568,69 @@
     </row>
     <row r="71" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="C71" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D71" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="C72" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D72" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="C73" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D73" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="C74" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D74" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>320</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D75" s="3">
         <v>45</v>
@@ -2713,13 +2638,13 @@
     </row>
     <row r="76" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D76" s="3">
         <v>45</v>
@@ -2727,111 +2652,111 @@
     </row>
     <row r="77" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>338</v>
+        <v>146</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D77" s="3">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>321</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D78" s="3">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>322</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D79" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>339</v>
+        <v>150</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D80" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>340</v>
+        <v>152</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D81" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D82" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D83" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D84" s="3">
         <v>40</v>
@@ -2839,13 +2764,13 @@
     </row>
     <row r="85" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D85" s="3">
         <v>40</v>
@@ -2853,153 +2778,153 @@
     </row>
     <row r="86" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D86" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>341</v>
+        <v>163</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D87" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>324</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D88" s="3">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>168</v>
+        <v>325</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D89" s="3">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D90" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>343</v>
+        <v>167</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D91" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D92" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D93" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>345</v>
+        <v>172</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D94" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="C95" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D95" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D96" s="3">
         <v>35</v>
@@ -3007,13 +2932,13 @@
     </row>
     <row r="97" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D97" s="3">
         <v>35</v>
@@ -3021,55 +2946,55 @@
     </row>
     <row r="98" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>329</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D98" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>330</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D99" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>346</v>
+        <v>180</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>331</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D100" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>347</v>
+        <v>181</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D101" s="3">
         <v>34</v>
@@ -3077,13 +3002,13 @@
     </row>
     <row r="102" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>348</v>
+        <v>184</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D102" s="3">
         <v>34</v>
@@ -3091,13 +3016,13 @@
     </row>
     <row r="103" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>349</v>
+        <v>185</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>332</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D103" s="3">
         <v>34</v>
@@ -3105,167 +3030,167 @@
     </row>
     <row r="104" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>333</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D104" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>191</v>
+        <v>334</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D105" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D106" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>351</v>
+        <v>189</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D107" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>352</v>
+        <v>191</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D108" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D109" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>337</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D110" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D111" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>354</v>
+        <v>197</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D112" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>355</v>
+        <v>199</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D113" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B114" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="C114" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D114" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>338</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D115" s="3">
         <v>30</v>
@@ -3273,83 +3198,83 @@
     </row>
     <row r="116" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>207</v>
+        <v>339</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D116" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>209</v>
+        <v>340</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D117" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>356</v>
+        <v>206</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D118" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>357</v>
+        <v>208</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>341</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D119" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>358</v>
+        <v>209</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>342</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D120" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D121" s="3">
         <v>28</v>
@@ -3357,125 +3282,125 @@
     </row>
     <row r="122" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D122" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D123" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D124" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>346</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D125" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>362</v>
+        <v>216</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D126" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D127" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D128" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D129" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>366</v>
+        <v>220</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>351</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D130" s="3">
         <v>26</v>
@@ -3483,13 +3408,13 @@
     </row>
     <row r="131" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>367</v>
+        <v>222</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D131" s="3">
         <v>26</v>
@@ -3497,13 +3422,13 @@
     </row>
     <row r="132" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D132" s="3">
         <v>26</v>
@@ -3511,13 +3436,13 @@
     </row>
     <row r="133" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D133" s="3">
         <v>26</v>
@@ -3525,13 +3450,13 @@
     </row>
     <row r="134" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D134" s="3">
         <v>26</v>
@@ -3539,13 +3464,13 @@
     </row>
     <row r="135" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D135" s="3">
         <v>26</v>
@@ -3553,13 +3478,13 @@
     </row>
     <row r="136" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D136" s="3">
         <v>26</v>
@@ -3567,13 +3492,13 @@
     </row>
     <row r="137" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D137" s="3">
         <v>26</v>
@@ -3581,97 +3506,97 @@
     </row>
     <row r="138" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D138" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D139" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D140" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>376</v>
+        <v>232</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D141" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>377</v>
+        <v>234</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D142" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D143" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D144" s="3">
         <v>24</v>
@@ -3679,13 +3604,13 @@
     </row>
     <row r="145" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>363</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D145" s="3">
         <v>24</v>
@@ -3693,69 +3618,69 @@
     </row>
     <row r="146" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>364</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D146" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D147" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D148" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D149" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D150" s="3">
         <v>23</v>
@@ -3763,13 +3688,13 @@
     </row>
     <row r="151" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>384</v>
+        <v>245</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D151" s="3">
         <v>23</v>
@@ -3777,125 +3702,125 @@
     </row>
     <row r="152" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D152" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D153" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>387</v>
+        <v>248</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D154" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>253</v>
+        <v>371</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D155" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D156" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D157" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>374</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D158" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D159" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D160" s="3">
         <v>21</v>
@@ -3903,13 +3828,13 @@
     </row>
     <row r="161" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D161" s="3">
         <v>21</v>
@@ -3917,181 +3842,181 @@
     </row>
     <row r="162" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D162" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D163" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D164" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>396</v>
+        <v>260</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>261</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D165" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>397</v>
+        <v>262</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>263</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D166" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D167" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>267</v>
+        <v>382</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D168" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D169" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>400</v>
+        <v>267</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D170" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>384</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D171" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>385</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D172" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D173" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D174" s="3">
         <v>18</v>
@@ -4099,97 +4024,97 @@
     </row>
     <row r="175" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D175" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>389</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D176" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D177" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D178" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D179" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D180" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>408</v>
+        <v>279</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D181" s="3">
         <v>17</v>
@@ -4197,13 +4122,13 @@
     </row>
     <row r="182" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D182" s="3">
         <v>17</v>
@@ -4211,13 +4136,13 @@
     </row>
     <row r="183" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D183" s="3">
         <v>17</v>
@@ -4225,153 +4150,153 @@
     </row>
     <row r="184" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D184" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D185" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D186" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>290</v>
+        <v>286</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D187" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D188" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D189" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D190" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D191" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D192" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D193" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D194" s="3">
         <v>15</v>
@@ -4379,477 +4304,295 @@
     </row>
     <row r="195" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D195" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>422</v>
+        <v>295</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D196" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D197" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D198" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D199" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B200" s="4" t="s">
-        <v>426</v>
+        <v>300</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>301</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D200" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D201" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D202" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>412</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D203" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D204" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D205" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D206" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>416</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D207" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D208" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B209" s="4" t="s">
-        <v>433</v>
+        <v>310</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>311</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D209" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="B210" s="4" t="s">
-        <v>434</v>
+        <v>312</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D210" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D211" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D212" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D213" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D214" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>320</v>
+        <v>422</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="D215" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A216" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D216" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A217" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D217" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A218" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D218" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A219" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B219" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D219" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A220" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B220" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="C220" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D220" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A221" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B221" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="C221" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D221" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A222" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B222" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D222" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A223" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D223" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A224" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D224" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A225" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B225" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D225" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A226" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B226" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D226" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A227" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D227" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A228" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="D228" s="3">
         <v>0</v>
       </c>
     </row>

--- a/support_files/ir_rating.xlsx
+++ b/support_files/ir_rating.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilyas\Documents\GitHub\invest_toolkit\support_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilya\Documents\MyDocs\02_github\invest_toolkit\support_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E660BD-F8BD-4B86-B1A9-8759D295A286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B380226-209B-4DFE-85C8-18702BA8416E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="432">
   <si>
     <t>name</t>
   </si>
@@ -1315,6 +1315,12 @@
   </si>
   <si>
     <t>VSYDP</t>
+  </si>
+  <si>
+    <t>ДОМРФ</t>
+  </si>
+  <si>
+    <t>DOMRF</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D215"/>
+  <dimension ref="A1:D216"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.44140625" style="1" customWidth="1"/>
@@ -2064,10 +2070,10 @@
     </row>
     <row r="35" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>67</v>
+        <v>430</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>68</v>
+        <v>431</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>425</v>
@@ -2078,24 +2084,24 @@
     </row>
     <row r="36" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D36" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>425</v>
@@ -2106,10 +2112,10 @@
     </row>
     <row r="38" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>425</v>
@@ -2120,38 +2126,38 @@
     </row>
     <row r="39" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D39" s="3">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D40" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>425</v>
@@ -2162,10 +2168,10 @@
     </row>
     <row r="42" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>425</v>
@@ -2176,24 +2182,24 @@
     </row>
     <row r="43" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D43" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>425</v>
@@ -2204,52 +2210,52 @@
     </row>
     <row r="45" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>318</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D45" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D46" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D47" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>425</v>
@@ -2260,94 +2266,94 @@
     </row>
     <row r="49" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D49" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D50" s="3">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>319</v>
+        <v>96</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D51" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>319</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D52" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D53" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D54" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>425</v>
@@ -2358,10 +2364,10 @@
     </row>
     <row r="56" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>425</v>
@@ -2372,24 +2378,24 @@
     </row>
     <row r="57" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D57" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>425</v>
@@ -2400,10 +2406,10 @@
     </row>
     <row r="59" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>425</v>
@@ -2414,66 +2420,66 @@
     </row>
     <row r="60" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D60" s="3">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D61" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D62" s="3">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D63" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>425</v>
@@ -2484,66 +2490,66 @@
     </row>
     <row r="65" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D65" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D66" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>427</v>
+        <v>127</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D67" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>427</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D68" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>425</v>
@@ -2554,10 +2560,10 @@
     </row>
     <row r="70" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>428</v>
+        <v>132</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>133</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>425</v>
@@ -2568,24 +2574,24 @@
     </row>
     <row r="71" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>428</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D71" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>425</v>
@@ -2596,24 +2602,24 @@
     </row>
     <row r="73" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D73" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>425</v>
@@ -2624,10 +2630,10 @@
     </row>
     <row r="75" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>320</v>
+        <v>141</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>425</v>
@@ -2638,10 +2644,10 @@
     </row>
     <row r="76" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>320</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>425</v>
@@ -2652,24 +2658,24 @@
     </row>
     <row r="77" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D77" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>321</v>
+        <v>146</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>425</v>
@@ -2680,24 +2686,24 @@
     </row>
     <row r="79" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D79" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>322</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>425</v>
@@ -2708,38 +2714,38 @@
     </row>
     <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D81" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D82" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>425</v>
@@ -2750,10 +2756,10 @@
     </row>
     <row r="84" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>425</v>
@@ -2764,10 +2770,10 @@
     </row>
     <row r="85" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>323</v>
+        <v>157</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>425</v>
@@ -2778,24 +2784,24 @@
     </row>
     <row r="86" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D86" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>425</v>
@@ -2806,38 +2812,38 @@
     </row>
     <row r="88" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>324</v>
+        <v>163</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D88" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D89" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>425</v>
@@ -2848,24 +2854,24 @@
     </row>
     <row r="91" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>326</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D91" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>327</v>
+        <v>167</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>425</v>
@@ -2876,24 +2882,24 @@
     </row>
     <row r="93" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>327</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D93" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>425</v>
@@ -2904,10 +2910,10 @@
     </row>
     <row r="95" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>425</v>
@@ -2918,10 +2924,10 @@
     </row>
     <row r="96" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>425</v>
@@ -2932,10 +2938,10 @@
     </row>
     <row r="97" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>328</v>
+        <v>176</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>425</v>
@@ -2946,24 +2952,24 @@
     </row>
     <row r="98" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D98" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>425</v>
@@ -2974,10 +2980,10 @@
     </row>
     <row r="100" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>331</v>
+        <v>179</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>330</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>425</v>
@@ -2988,10 +2994,10 @@
     </row>
     <row r="101" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>182</v>
+        <v>331</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>425</v>
@@ -3002,10 +3008,10 @@
     </row>
     <row r="102" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>425</v>
@@ -3016,10 +3022,10 @@
     </row>
     <row r="103" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>332</v>
+        <v>184</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>425</v>
@@ -3030,24 +3036,24 @@
     </row>
     <row r="104" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D104" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>425</v>
@@ -3058,10 +3064,10 @@
     </row>
     <row r="106" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>425</v>
@@ -3072,24 +3078,24 @@
     </row>
     <row r="107" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>335</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D107" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>425</v>
@@ -3100,10 +3106,10 @@
     </row>
     <row r="109" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>336</v>
+        <v>191</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>425</v>
@@ -3114,24 +3120,24 @@
     </row>
     <row r="110" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D110" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>337</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>425</v>
@@ -3142,24 +3148,24 @@
     </row>
     <row r="112" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D112" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>425</v>
@@ -3170,10 +3176,10 @@
     </row>
     <row r="114" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>425</v>
@@ -3184,10 +3190,10 @@
     </row>
     <row r="115" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>338</v>
+        <v>201</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>425</v>
@@ -3198,24 +3204,24 @@
     </row>
     <row r="116" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>339</v>
+        <v>203</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>338</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D116" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>425</v>
@@ -3226,24 +3232,24 @@
     </row>
     <row r="118" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>207</v>
+        <v>340</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D118" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>341</v>
+        <v>206</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>425</v>
@@ -3254,10 +3260,10 @@
     </row>
     <row r="120" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>425</v>
@@ -3268,10 +3274,10 @@
     </row>
     <row r="121" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>342</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>425</v>
@@ -3282,24 +3288,24 @@
     </row>
     <row r="122" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>343</v>
+        <v>210</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D122" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>425</v>
@@ -3310,10 +3316,10 @@
     </row>
     <row r="124" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>425</v>
@@ -3324,10 +3330,10 @@
     </row>
     <row r="125" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>425</v>
@@ -3338,24 +3344,24 @@
     </row>
     <row r="126" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>347</v>
+        <v>215</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>346</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D126" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>348</v>
+        <v>216</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>425</v>
@@ -3366,10 +3372,10 @@
     </row>
     <row r="128" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>425</v>
@@ -3380,10 +3386,10 @@
     </row>
     <row r="129" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>425</v>
@@ -3394,10 +3400,10 @@
     </row>
     <row r="130" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>425</v>
@@ -3408,10 +3414,10 @@
     </row>
     <row r="131" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>222</v>
+        <v>351</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>425</v>
@@ -3422,10 +3428,10 @@
     </row>
     <row r="132" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>352</v>
+        <v>222</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>425</v>
@@ -3436,10 +3442,10 @@
     </row>
     <row r="133" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>425</v>
@@ -3450,10 +3456,10 @@
     </row>
     <row r="134" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>425</v>
@@ -3464,10 +3470,10 @@
     </row>
     <row r="135" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>425</v>
@@ -3478,10 +3484,10 @@
     </row>
     <row r="136" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>425</v>
@@ -3492,10 +3498,10 @@
     </row>
     <row r="137" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>425</v>
@@ -3506,24 +3512,24 @@
     </row>
     <row r="138" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D138" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>425</v>
@@ -3534,24 +3540,24 @@
     </row>
     <row r="140" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D140" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>360</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>425</v>
@@ -3562,10 +3568,10 @@
     </row>
     <row r="142" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>425</v>
@@ -3576,10 +3582,10 @@
     </row>
     <row r="143" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>361</v>
+        <v>234</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>425</v>
@@ -3590,10 +3596,10 @@
     </row>
     <row r="144" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>425</v>
@@ -3604,10 +3610,10 @@
     </row>
     <row r="145" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>425</v>
@@ -3618,24 +3624,24 @@
     </row>
     <row r="146" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D146" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>425</v>
@@ -3646,10 +3652,10 @@
     </row>
     <row r="148" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>425</v>
@@ -3660,10 +3666,10 @@
     </row>
     <row r="149" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>425</v>
@@ -3674,10 +3680,10 @@
     </row>
     <row r="150" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>425</v>
@@ -3688,10 +3694,10 @@
     </row>
     <row r="151" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>245</v>
+        <v>368</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>425</v>
@@ -3702,24 +3708,24 @@
     </row>
     <row r="152" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>369</v>
+        <v>245</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D152" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>425</v>
@@ -3730,10 +3736,10 @@
     </row>
     <row r="154" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>370</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>425</v>
@@ -3744,10 +3750,10 @@
     </row>
     <row r="155" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>371</v>
+        <v>248</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>425</v>
@@ -3758,24 +3764,24 @@
     </row>
     <row r="156" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D156" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>425</v>
@@ -3786,10 +3792,10 @@
     </row>
     <row r="158" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>425</v>
@@ -3800,10 +3806,10 @@
     </row>
     <row r="159" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>425</v>
@@ -3814,10 +3820,10 @@
     </row>
     <row r="160" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>425</v>
@@ -3828,10 +3834,10 @@
     </row>
     <row r="161" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>425</v>
@@ -3842,24 +3848,24 @@
     </row>
     <row r="162" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D162" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>425</v>
@@ -3870,10 +3876,10 @@
     </row>
     <row r="164" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>425</v>
@@ -3884,10 +3890,10 @@
     </row>
     <row r="165" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>380</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>425</v>
@@ -3898,24 +3904,24 @@
     </row>
     <row r="166" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>261</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D166" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>381</v>
+        <v>262</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>263</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>425</v>
@@ -3926,24 +3932,24 @@
     </row>
     <row r="168" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D168" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>425</v>
@@ -3954,10 +3960,10 @@
     </row>
     <row r="170" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>383</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>425</v>
@@ -3968,10 +3974,10 @@
     </row>
     <row r="171" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>384</v>
+        <v>267</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>425</v>
@@ -3982,10 +3988,10 @@
     </row>
     <row r="172" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>425</v>
@@ -3996,10 +4002,10 @@
     </row>
     <row r="173" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>425</v>
@@ -4010,10 +4016,10 @@
     </row>
     <row r="174" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>425</v>
@@ -4024,24 +4030,24 @@
     </row>
     <row r="175" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D175" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>425</v>
@@ -4052,10 +4058,10 @@
     </row>
     <row r="177" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>425</v>
@@ -4066,10 +4072,10 @@
     </row>
     <row r="178" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>425</v>
@@ -4080,10 +4086,10 @@
     </row>
     <row r="179" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>425</v>
@@ -4094,10 +4100,10 @@
     </row>
     <row r="180" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>425</v>
@@ -4108,10 +4114,10 @@
     </row>
     <row r="181" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>393</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>425</v>
@@ -4122,10 +4128,10 @@
     </row>
     <row r="182" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>394</v>
+        <v>279</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>425</v>
@@ -4136,10 +4142,10 @@
     </row>
     <row r="183" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>425</v>
@@ -4150,24 +4156,24 @@
     </row>
     <row r="184" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D184" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>425</v>
@@ -4178,10 +4184,10 @@
     </row>
     <row r="186" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>425</v>
@@ -4192,10 +4198,10 @@
     </row>
     <row r="187" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>425</v>
@@ -4206,24 +4212,24 @@
     </row>
     <row r="188" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D188" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>425</v>
@@ -4234,10 +4240,10 @@
     </row>
     <row r="190" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>425</v>
@@ -4248,10 +4254,10 @@
     </row>
     <row r="191" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>425</v>
@@ -4262,10 +4268,10 @@
     </row>
     <row r="192" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>425</v>
@@ -4276,10 +4282,10 @@
     </row>
     <row r="193" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>425</v>
@@ -4290,10 +4296,10 @@
     </row>
     <row r="194" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>425</v>
@@ -4304,24 +4310,24 @@
     </row>
     <row r="195" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D195" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>406</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>425</v>
@@ -4332,10 +4338,10 @@
     </row>
     <row r="197" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>407</v>
+        <v>295</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>425</v>
@@ -4346,10 +4352,10 @@
     </row>
     <row r="198" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>425</v>
@@ -4360,10 +4366,10 @@
     </row>
     <row r="199" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>425</v>
@@ -4374,24 +4380,24 @@
     </row>
     <row r="200" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>409</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D200" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B201" s="4" t="s">
-        <v>410</v>
+        <v>300</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>301</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>425</v>
@@ -4402,10 +4408,10 @@
     </row>
     <row r="202" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>425</v>
@@ -4416,10 +4422,10 @@
     </row>
     <row r="203" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>425</v>
@@ -4430,24 +4436,24 @@
     </row>
     <row r="204" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D204" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>425</v>
@@ -4458,24 +4464,24 @@
     </row>
     <row r="206" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D206" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>425</v>
@@ -4486,24 +4492,24 @@
     </row>
     <row r="208" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D208" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>417</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>425</v>
@@ -4514,10 +4520,10 @@
     </row>
     <row r="210" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>425</v>
@@ -4528,38 +4534,38 @@
     </row>
     <row r="211" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B211" s="4" t="s">
-        <v>418</v>
+        <v>312</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D211" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D212" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>425</v>
@@ -4570,10 +4576,10 @@
     </row>
     <row r="214" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>425</v>
@@ -4584,15 +4590,29 @@
     </row>
     <row r="215" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D215" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B216" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="C215" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="D215" s="3">
+      <c r="C216" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D216" s="3">
         <v>0</v>
       </c>
     </row>
